--- a/agenda/data/schedule.xlsx
+++ b/agenda/data/schedule.xlsx
@@ -19,19 +19,19 @@
     <r>
       <rPr>
         <b/>
-        <sz val="7.5"/>
+        <sz val="8.0"/>
         <color rgb="FFFFFFFF"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">SEMANA PADRÃO 8º PERÍODO - 2.2026 - 61  alunos</t>
+      <t xml:space="preserve">SEMANA PADRÃO 8º PERÍODO - 2.2026 - 65  alunos</t>
     </r>
   </si>
   <si>
     <r>
       <rPr>
         <b/>
-        <sz val="7.5"/>
+        <sz val="8.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -174,7 +174,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Isnaya Araujo - 3/4</t>
+      <t xml:space="preserve">Isnaya Araujo - 2/1</t>
     </r>
   </si>
   <si>
@@ -194,17 +194,17 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Priscila Monteiro - 1/2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alexandre Filipov - 7/8</t>
+      <t xml:space="preserve">Priscila Monteiro - 6/5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alexandre Filipov - 5/6</t>
     </r>
   </si>
   <si>
@@ -225,7 +225,18 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Tainan Ramos - 4/3</t>
+      <t xml:space="preserve">Tainan Ramos - 7/8</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">CI PRATICA - POLIMEG</t>
     </r>
   </si>
   <si>
@@ -246,27 +257,27 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Roberta Mota - 5/6</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Daniela Leão - 8/7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Adriano Monteiro - 6/5</t>
+      <t xml:space="preserve">Roberta Mota -9/10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Daniela Leão - 9/10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Adriano Monteiro - 4/3</t>
     </r>
   </si>
   <si>
@@ -283,12 +294,82 @@
   <si>
     <r>
       <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Daniela Matiolli - 8/7</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">08:00-08:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 03 - Profa. Kênia</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ivina  - Grupos 1/2</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b/>
         <sz val="5.5"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">CI PRATICA - POLIMEG</t>
+      <t xml:space="preserve">CI PRATICA - Casa da Criança</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">10:50 - 12:30</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">GRUPO 2 - Michel Batista</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Ivina - Grupos 3/4</t>
     </r>
   </si>
   <si>
@@ -298,17 +379,7 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Daniela Matiolli - 2/1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">08:00-08:50</t>
+      <t xml:space="preserve">Grupo 04 - Prof. Lucas Amaral</t>
     </r>
   </si>
   <si>
@@ -318,47 +389,17 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Grupo 03 - Profa. Kênia</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ivina  - Grupos 9/10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:50 - 12:30</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">GRUPO 2 - Michel Batista</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Ivina - Grupos 7/8</t>
+      <t xml:space="preserve">Karla Baleeiro - 6/5</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">09:00-09:50</t>
     </r>
   </si>
   <si>
@@ -368,7 +409,7 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Grupo 04 - Prof. Lucas Amaral</t>
+      <t xml:space="preserve">Grupo 01 - Prof. Lucas Amaral</t>
     </r>
   </si>
   <si>
@@ -378,7 +419,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">09:00-09:50</t>
+      <t xml:space="preserve">10:00-10:50</t>
     </r>
   </si>
   <si>
@@ -388,26 +429,6 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Grupo 01 - Prof. Lucas Amaral</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">10:00-10:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve">Grupo 02 - Prof. Lucas Amaral</t>
     </r>
   </si>
@@ -415,7 +436,7 @@
     <r>
       <rPr>
         <b/>
-        <sz val="7.5"/>
+        <sz val="8.0"/>
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
@@ -470,7 +491,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Lenilson Prates 9/10</t>
+      <t xml:space="preserve">Lenilson Prates - 8/7</t>
     </r>
   </si>
   <si>
@@ -490,7 +511,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Roberta - 10/9</t>
+      <t xml:space="preserve">Roberta Mota - 7/8</t>
     </r>
   </si>
   <si>
@@ -511,17 +532,17 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Thiara Prates  - 2/1</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Alexandre Filipov - 4/3</t>
+      <t xml:space="preserve">Thiara Prates  - 5/6</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Alexandre Filipov - 1/2</t>
     </r>
   </si>
   <si>
@@ -541,17 +562,17 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">Luane Costa - 3/4</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Daniela Leão -  5/6</t>
+      <t xml:space="preserve">Luane Costa - 10/9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Daniela Leão -  2/1</t>
     </r>
   </si>
   <si>
@@ -582,7 +603,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">CI PRATICA - Casa da Criança</t>
+      <t xml:space="preserve">COMUNIDADES - PRÁTICA</t>
     </r>
   </si>
   <si>
@@ -593,7 +614,7 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">COMUNIDADES - PRÁTICA</t>
+      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - MARC</t>
     </r>
   </si>
   <si>
@@ -604,7 +625,107 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - MARC</t>
+      <t xml:space="preserve">HAM - PALESTRA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">13:50-18:00</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Priscila Monteiro - 4/3</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">14:00 - 18:10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Isnaya Araujo - 10/9</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:00 - 18:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 01  - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">15:00 - 16:05</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prof. Adriano Monteiro</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">TODOS - Prof. Michel Batista</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">16:25 - 17:25</t>
     </r>
   </si>
   <si>
@@ -615,7 +736,28 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">HAM - PALESTRA</t>
+      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - PALESTRA</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="5.5"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">MOMENTO NED (mensal)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">17:30 - 18:20</t>
     </r>
   </si>
   <si>
@@ -625,57 +767,17 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Karla Baleeiro - 1/2</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">14:00 - 18:10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Isnaya Araujo - 6/5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:00 - 18:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 01  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">15:00 - 16:05</t>
+      <t xml:space="preserve">Prof. Adriano Monteiro, Profa. Naira e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:00 - 19:05</t>
     </r>
   </si>
   <si>
@@ -685,37 +787,125 @@
         <rFont val="Trebuchet MS"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:0 - 18:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">TODOS - Prof. Michel Batista</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">16:25 - 17:25</t>
+      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Christielle - 3/4</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:00 - 19:50                     Grupo 02  - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">19:25 - 20:25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:30 - 21:20</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prof. Marcelo</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">20:00 - 20:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 03 - Profa. Agnis de Jesus</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">18:20 - 19:25</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Profa. Naira e Prof. Iomar</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira e
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Trebuchet MS"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Prof. Iomar</t>
     </r>
   </si>
   <si>
@@ -726,128 +916,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">CLÍNICA INTEGRADA - CI - PALESTRA</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">MOMENTO NED (mensal)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">17:30 - 18:20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro, Profa. Naira e Prof. Iomar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">13:50-18:00</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Priscila Monteiro - 10/9</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Christielle - 8/7</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:00 - 19:50                     Grupo 02  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">18:20 - 19:25</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Profa. Naira e Prof. Iomar</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">20:30 - 21:20</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Prof. Marcelo</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="5.5"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t xml:space="preserve">IESC - PALESTRA</t>
     </r>
   </si>
@@ -858,26 +926,6 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">20:00 - 20:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 03 - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
       <t xml:space="preserve">19:45 - 20:25</t>
     </r>
   </si>
@@ -888,26 +936,17 @@
         <rFont val="Calibri"/>
         <family val="1"/>
       </rPr>
-      <t xml:space="preserve">18:00 - 19:05</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Prof. Adriano Monteiro, Profa Naira
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Trebuchet MS"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">e Prof. Iomar</t>
+      <t xml:space="preserve">21:00 - 21:50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="4.0"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">Grupo 04  - Profa. Agnis de Jesus</t>
     </r>
   </si>
   <si>
@@ -928,36 +967,6 @@
         <family val="1"/>
       </rPr>
       <t xml:space="preserve">Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">21:00 - 21:50</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">Grupo 04  - Profa. Agnis de Jesus</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="4.0"/>
-        <rFont val="Calibri"/>
-        <family val="1"/>
-      </rPr>
-      <t xml:space="preserve">19:25 - 20:25</t>
     </r>
   </si>
 </sst>
@@ -975,7 +984,7 @@
     </font>
     <font>
       <b/>
-      <sz val="7.5"/>
+      <sz val="8"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1226,7 +1235,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="186">
     <xf numFmtId="0" fillId="0" borderId="0" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1320,252 +1329,231 @@
     <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="8" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="9" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="10" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="8" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="9" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="7" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="11" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="12" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="13" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="11" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="12" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="13" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="8" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="9" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="8" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="9" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="10" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="6" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="4" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="6" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="8" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="9" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="10" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="7" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="8" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="9" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="11" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="11" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="12" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="13" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="12" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="13" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="0" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="8" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="9" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="10" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="11" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="12" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="6" borderId="13" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="5" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="4" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="2" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
@@ -1575,6 +1563,12 @@
     <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fillId="5" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fillId="8" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1656,44 +1650,32 @@
     <xf numFmtId="0" fillId="9" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="5" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="5" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="5" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" indent="4" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="8" borderId="8" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -1716,23 +1698,47 @@
     <xf numFmtId="0" fillId="9" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="4" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" indent="1" wrapText="1"/>
+    <xf numFmtId="0" fillId="9" borderId="5" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="6" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fillId="8" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="9" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="8" borderId="1" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1743,8 +1749,8 @@
     <xf numFmtId="0" fillId="8" borderId="4" fontId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="8" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fillId="8" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="9" borderId="1" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
@@ -1755,20 +1761,11 @@
     <xf numFmtId="0" fillId="9" borderId="7" fontId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="3" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="9" borderId="1" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="5" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="3" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="6" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="bottom" indent="3" wrapText="1"/>
+    <xf numFmtId="0" fillId="8" borderId="5" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="6" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="8" borderId="2" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" indent="2" wrapText="1"/>
@@ -1786,13 +1783,16 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fillId="0" borderId="14" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="8" borderId="7" fontId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fillId="0" borderId="10" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fillId="8" borderId="7" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fillId="8" borderId="6" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fillId="0" borderId="0" fontId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2088,22 +2088,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" customWidth="1" width="10.666667"/>
-    <col min="2" max="2" customWidth="1" width="25.777778"/>
-    <col min="3" max="3" customWidth="1" width="15.555556"/>
-    <col min="4" max="4" customWidth="1" width="16.444444"/>
-    <col min="5" max="5" customWidth="1" width="8.444444"/>
-    <col min="6" max="6" customWidth="1" width="21.111111"/>
-    <col min="7" max="7" customWidth="1" width="7.333333"/>
-    <col min="8" max="8" customWidth="1" width="24.444444"/>
-    <col min="9" max="9" customWidth="1" width="7.777778"/>
-    <col min="10" max="10" customWidth="1" width="22.888889"/>
+    <col min="1" max="1" customWidth="1" width="11.111111"/>
+    <col min="2" max="2" customWidth="1" width="27.333333"/>
+    <col min="3" max="3" customWidth="1" width="16.444444"/>
+    <col min="4" max="4" customWidth="1" width="17.555556"/>
+    <col min="5" max="5" customWidth="1" width="8.888889"/>
+    <col min="6" max="6" customWidth="1" width="22.444444"/>
+    <col min="7" max="7" customWidth="1" width="7.777778"/>
+    <col min="8" max="8" customWidth="1" width="25.777778"/>
+    <col min="9" max="9" customWidth="1" width="8.222222"/>
+    <col min="10" max="10" customWidth="1" width="24.444444"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="11.50" customHeight="1">
+    <row r="1" spans="1:10" ht="12.25" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="I1" s="3"/>
       <c r="J1" s="4"/>
     </row>
-    <row r="2" spans="1:10" ht="11.25" customHeight="1">
+    <row r="2" spans="1:10" ht="12.00" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2175,7 +2175,7 @@
       </c>
       <c r="J4" s="20"/>
     </row>
-    <row r="5" spans="1:10" ht="11.25" customHeight="1">
+    <row r="5" spans="1:10" ht="12.00" customHeight="1">
       <c r="A5" s="22" t="s">
         <v>11</v>
       </c>
@@ -2188,10 +2188,10 @@
       <c r="D5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="32" t="s">
+      <c r="F5" s="30" t="s">
         <v>16</v>
       </c>
       <c r="G5" s="30" t="s">
@@ -2210,14 +2210,14 @@
     <row r="6" spans="1:10" ht="8.25" customHeight="1">
       <c r="A6" s="23"/>
       <c r="B6" s="27"/>
-      <c r="C6" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="34" t="s">
+      <c r="C6" s="32" t="s">
         <v>20</v>
       </c>
-      <c r="F6" s="35"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="35" t="s">
+        <v>21</v>
+      </c>
+      <c r="F6" s="36"/>
       <c r="G6" s="16" t="s">
         <v>8</v>
       </c>
@@ -2227,28 +2227,28 @@
       </c>
       <c r="J6" s="17"/>
     </row>
-    <row r="7" spans="1:10" ht="11.25" customHeight="1">
+    <row r="7" spans="1:10" ht="12.00" customHeight="1">
       <c r="A7" s="23"/>
       <c r="B7" s="27"/>
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="37"/>
+        <v>22</v>
+      </c>
+      <c r="E7" s="37"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="30" t="s">
         <v>15</v>
       </c>
       <c r="H7" s="30" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I7" s="30" t="s">
         <v>15</v>
       </c>
       <c r="J7" s="30" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10" ht="8.25" customHeight="1">
@@ -2258,18 +2258,18 @@
         <v>8</v>
       </c>
       <c r="D8" s="17"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="40"/>
-      <c r="I8" s="42" t="s">
+      <c r="E8" s="37"/>
+      <c r="F8" s="38"/>
+      <c r="G8" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="J8" s="43"/>
-    </row>
-    <row r="9" spans="1:10" ht="11.25" customHeight="1">
+      <c r="H8" s="41"/>
+      <c r="I8" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J8" s="33"/>
+    </row>
+    <row r="9" spans="1:10" ht="12.00" customHeight="1">
       <c r="A9" s="24"/>
       <c r="B9" s="28"/>
       <c r="C9" s="29" t="s">
@@ -2278,12 +2278,12 @@
       <c r="D9" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="36"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="44" t="s">
+      <c r="E9" s="37"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="43" t="s">
         <v>28</v>
       </c>
       <c r="I9" s="30" t="s">
@@ -2298,92 +2298,98 @@
         <v>7</v>
       </c>
       <c r="B10" s="14"/>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D10" s="33"/>
+      <c r="E10" s="37"/>
+      <c r="F10" s="38"/>
+      <c r="G10" s="40" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="43"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="40"/>
-      <c r="I10" s="47"/>
-      <c r="J10" s="48"/>
-    </row>
-    <row r="11" spans="1:10" ht="14.50" customHeight="1">
+      <c r="H10" s="41"/>
+      <c r="I10" s="45" t="s">
+        <v>30</v>
+      </c>
+      <c r="J10" s="46"/>
+    </row>
+    <row r="11" spans="1:10" ht="12.00" customHeight="1">
       <c r="A11" s="22" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C11" s="29" t="s">
         <v>13</v>
       </c>
       <c r="D11" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="44" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="37"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="45" t="s">
-        <v>33</v>
-      </c>
-      <c r="I11" s="49"/>
-      <c r="J11" s="50"/>
+      <c r="H11" s="43" t="s">
+        <v>34</v>
+      </c>
+      <c r="I11" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="J11" s="51" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="8.25" customHeight="1">
       <c r="A12" s="23"/>
       <c r="B12" s="27"/>
-      <c r="C12" s="39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D12" s="40"/>
-      <c r="E12" s="52"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="47"/>
-      <c r="H12" s="48"/>
+      <c r="C12" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12" s="41"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="54"/>
+      <c r="H12" s="55"/>
       <c r="I12" s="49"/>
-      <c r="J12" s="50"/>
-    </row>
-    <row r="13" spans="1:10" ht="14.50" customHeight="1">
+      <c r="J12" s="52"/>
+    </row>
+    <row r="13" spans="1:10" ht="15.25" customHeight="1">
       <c r="A13" s="23"/>
       <c r="B13" s="27"/>
-      <c r="C13" s="44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D13" s="45" t="s">
-        <v>35</v>
-      </c>
-      <c r="E13" s="52"/>
-      <c r="F13" s="53"/>
-      <c r="G13" s="49"/>
-      <c r="H13" s="50"/>
-      <c r="I13" s="49"/>
-      <c r="J13" s="50"/>
-    </row>
-    <row r="14" spans="1:10" ht="11.50" customHeight="1">
+      <c r="C13" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="56" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="63"/>
+      <c r="H13" s="64"/>
+      <c r="I13" s="68"/>
+      <c r="J13" s="69"/>
+    </row>
+    <row r="14" spans="1:10" ht="12.00" customHeight="1">
       <c r="A14" s="24"/>
       <c r="B14" s="28"/>
-      <c r="C14" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>37</v>
-      </c>
-      <c r="E14" s="54"/>
-      <c r="F14" s="55"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="58"/>
-    </row>
-    <row r="15" spans="1:10" ht="11.25" customHeight="1">
+      <c r="C14" s="42" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14" s="43" t="s">
+        <v>39</v>
+      </c>
+      <c r="E14" s="60"/>
+      <c r="F14" s="61"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="65"/>
+      <c r="J14" s="66"/>
+    </row>
+    <row r="15" spans="1:10" ht="12.00" customHeight="1">
       <c r="A15" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B15" s="7"/>
       <c r="C15" s="7"/>
@@ -2404,56 +2410,56 @@
         <v>8</v>
       </c>
       <c r="D16" s="17"/>
-      <c r="E16" s="61" t="s">
-        <v>39</v>
-      </c>
-      <c r="F16" s="62"/>
-      <c r="G16" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="H16" s="43"/>
-      <c r="I16" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="43"/>
-    </row>
-    <row r="17" spans="1:10" ht="17.25" customHeight="1">
-      <c r="A17" s="68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B17" s="71" t="s">
+      <c r="E16" s="71" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="73" t="s">
+      <c r="F16" s="72"/>
+      <c r="G16" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="33"/>
+      <c r="I16" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="33"/>
+    </row>
+    <row r="17" spans="1:10" ht="18.50" customHeight="1">
+      <c r="A17" s="22" t="s">
         <v>42</v>
       </c>
-      <c r="D17" s="74" t="s">
+      <c r="B17" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="63"/>
-      <c r="F17" s="64"/>
-      <c r="G17" s="73" t="s">
+      <c r="C17" s="77" t="s">
         <v>44</v>
       </c>
-      <c r="H17" s="74" t="s">
+      <c r="D17" s="78" t="s">
         <v>45</v>
       </c>
-      <c r="I17" s="73" t="s">
+      <c r="E17" s="73"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="77" t="s">
         <v>46</v>
       </c>
-      <c r="J17" s="74" t="s">
+      <c r="H17" s="78" t="s">
         <v>47</v>
       </c>
+      <c r="I17" s="77" t="s">
+        <v>48</v>
+      </c>
+      <c r="J17" s="78" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A18" s="69"/>
-      <c r="B18" s="72"/>
-      <c r="C18" s="42" t="s">
-        <v>25</v>
-      </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="64"/>
+      <c r="A18" s="24"/>
+      <c r="B18" s="28"/>
+      <c r="C18" s="32" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="33"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="74"/>
       <c r="G18" s="16" t="s">
         <v>8</v>
       </c>
@@ -2468,302 +2474,284 @@
         <v>7</v>
       </c>
       <c r="B19" s="14"/>
-      <c r="C19" s="76" t="s">
-        <v>42</v>
-      </c>
-      <c r="D19" s="79" t="s">
+      <c r="C19" s="80" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="83" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="48" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="85" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="88" t="s">
         <v>48</v>
       </c>
-      <c r="E19" s="63"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="82" t="s">
-        <v>49</v>
-      </c>
-      <c r="H19" s="84" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="87" t="s">
-        <v>46</v>
-      </c>
-      <c r="J19" s="90" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" ht="11.25" customHeight="1">
-      <c r="A20" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B20" s="26" t="s">
+      <c r="J19" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="77"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="65"/>
-      <c r="F20" s="66"/>
-      <c r="G20" s="83"/>
-      <c r="H20" s="85"/>
-      <c r="I20" s="88"/>
-      <c r="J20" s="91"/>
+    </row>
+    <row r="20" spans="1:10" ht="12.00" customHeight="1">
+      <c r="A20" s="94" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" s="97" t="s">
+        <v>55</v>
+      </c>
+      <c r="C20" s="81"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="75"/>
+      <c r="F20" s="76"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="86"/>
+      <c r="I20" s="89"/>
+      <c r="J20" s="92"/>
     </row>
     <row r="21" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="93" t="s">
-        <v>54</v>
-      </c>
-      <c r="D21" s="94"/>
-      <c r="E21" s="19" t="s">
+      <c r="A21" s="95"/>
+      <c r="B21" s="98"/>
+      <c r="C21" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="F21" s="20"/>
-      <c r="G21" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="97"/>
-      <c r="I21" s="99" t="s">
+      <c r="D21" s="17"/>
+      <c r="E21" s="16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="17"/>
+      <c r="G21" s="100" t="s">
         <v>56</v>
       </c>
-      <c r="J21" s="100"/>
+      <c r="H21" s="101"/>
+      <c r="I21" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="J21" s="104"/>
     </row>
     <row r="22" spans="1:10" ht="8.25" customHeight="1">
       <c r="A22" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="14"/>
+      <c r="C22" s="106" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="E22" s="48" t="s">
+        <v>61</v>
+      </c>
+      <c r="F22" s="106" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" s="112" t="s">
+        <v>63</v>
+      </c>
+      <c r="H22" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="I22" s="119" t="s">
+        <v>65</v>
+      </c>
+      <c r="J22" s="120" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" ht="6.75" customHeight="1">
+      <c r="A23" s="94" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="107"/>
+      <c r="D23" s="109"/>
+      <c r="E23" s="110"/>
+      <c r="F23" s="107"/>
+      <c r="G23" s="113"/>
+      <c r="H23" s="117"/>
+      <c r="I23" s="119" t="s">
+        <v>68</v>
+      </c>
+      <c r="J23" s="120" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A24" s="95"/>
+      <c r="B24" s="123"/>
+      <c r="C24" s="108"/>
+      <c r="D24" s="84"/>
+      <c r="E24" s="49"/>
+      <c r="F24" s="108"/>
+      <c r="G24" s="114"/>
+      <c r="H24" s="118"/>
+      <c r="I24" s="125" t="s">
+        <v>69</v>
+      </c>
+      <c r="J24" s="126"/>
+    </row>
+    <row r="25" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A25" s="128" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="129"/>
+      <c r="C25" s="103" t="s">
         <v>57</v>
       </c>
-      <c r="B22" s="14"/>
-      <c r="C22" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" s="106" t="s">
-        <v>58</v>
-      </c>
-      <c r="E22" s="110" t="s">
-        <v>59</v>
-      </c>
-      <c r="F22" s="113" t="s">
-        <v>60</v>
-      </c>
-      <c r="G22" s="117" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="121" t="s">
-        <v>62</v>
-      </c>
-      <c r="I22" s="124" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="125" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A23" s="68" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="127" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="103"/>
-      <c r="D23" s="107"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="114"/>
-      <c r="G23" s="118"/>
-      <c r="H23" s="122"/>
-      <c r="I23" s="124" t="s">
-        <v>67</v>
-      </c>
-      <c r="J23" s="125" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A24" s="69"/>
-      <c r="B24" s="128"/>
-      <c r="C24" s="104"/>
-      <c r="D24" s="108"/>
-      <c r="E24" s="112"/>
-      <c r="F24" s="115"/>
-      <c r="G24" s="119"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="130" t="s">
-        <v>68</v>
-      </c>
-      <c r="J24" s="131"/>
-    </row>
-    <row r="25" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A25" s="133" t="s">
+      <c r="D25" s="104"/>
+      <c r="E25" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F25" s="17"/>
+      <c r="G25" s="100" t="s">
+        <v>56</v>
+      </c>
+      <c r="H25" s="101"/>
+      <c r="I25" s="133" t="s">
+        <v>71</v>
+      </c>
+      <c r="J25" s="136" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" ht="13.75" customHeight="1">
+      <c r="A26" s="130"/>
+      <c r="B26" s="131"/>
+      <c r="C26" s="119" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="138" t="s">
+        <v>74</v>
+      </c>
+      <c r="E26" s="140" t="s">
+        <v>44</v>
+      </c>
+      <c r="F26" s="144" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="147" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="148"/>
+      <c r="I26" s="134"/>
+      <c r="J26" s="137"/>
+    </row>
+    <row r="27" spans="1:10" ht="13.75" customHeight="1">
+      <c r="A27" s="152" t="s">
         <v>69</v>
       </c>
-      <c r="B25" s="134"/>
-      <c r="C25" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="17"/>
-      <c r="G25" s="96" t="s">
-        <v>55</v>
-      </c>
-      <c r="H25" s="97"/>
-      <c r="I25" s="138" t="s">
-        <v>70</v>
-      </c>
-      <c r="J25" s="141" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" ht="5.75" customHeight="1">
-      <c r="A26" s="135"/>
-      <c r="B26" s="136"/>
-      <c r="C26" s="143" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="146" t="s">
-        <v>73</v>
-      </c>
-      <c r="E26" s="150" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="153" t="s">
+      <c r="B27" s="153"/>
+      <c r="C27" s="119" t="s">
+        <v>77</v>
+      </c>
+      <c r="D27" s="138" t="s">
         <v>74</v>
       </c>
-      <c r="G26" s="156" t="s">
-        <v>75</v>
-      </c>
-      <c r="H26" s="157"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="142"/>
-    </row>
-    <row r="27" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A27" s="161" t="s">
-        <v>68</v>
-      </c>
-      <c r="B27" s="162"/>
-      <c r="C27" s="144"/>
-      <c r="D27" s="147"/>
-      <c r="E27" s="151"/>
-      <c r="F27" s="154"/>
-      <c r="G27" s="158"/>
-      <c r="H27" s="159"/>
-      <c r="I27" s="99" t="s">
-        <v>56</v>
-      </c>
-      <c r="J27" s="100"/>
-    </row>
-    <row r="28" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A28" s="163"/>
-      <c r="B28" s="163"/>
-      <c r="C28" s="145"/>
-      <c r="D28" s="148"/>
-      <c r="E28" s="152"/>
-      <c r="F28" s="155"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="164"/>
-      <c r="I28" s="124" t="s">
-        <v>76</v>
-      </c>
-      <c r="J28" s="125" t="s">
-        <v>77</v>
+      <c r="E27" s="141"/>
+      <c r="F27" s="145"/>
+      <c r="G27" s="149"/>
+      <c r="H27" s="150"/>
+      <c r="I27" s="103" t="s">
+        <v>57</v>
+      </c>
+      <c r="J27" s="104"/>
+    </row>
+    <row r="28" spans="1:10" ht="8.25" customHeight="1">
+      <c r="A28" s="155" t="s">
+        <v>78</v>
+      </c>
+      <c r="B28" s="158" t="s">
+        <v>79</v>
+      </c>
+      <c r="C28" s="103" t="s">
+        <v>69</v>
+      </c>
+      <c r="D28" s="104"/>
+      <c r="E28" s="142"/>
+      <c r="F28" s="146"/>
+      <c r="G28" s="161" t="s">
+        <v>80</v>
+      </c>
+      <c r="H28" s="161" t="s">
+        <v>81</v>
+      </c>
+      <c r="I28" s="119" t="s">
+        <v>82</v>
+      </c>
+      <c r="J28" s="120" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A29" s="166" t="s">
+      <c r="A29" s="156"/>
+      <c r="B29" s="159"/>
+      <c r="C29" s="163" t="s">
         <v>78</v>
       </c>
-      <c r="B29" s="168" t="s">
-        <v>79</v>
-      </c>
-      <c r="C29" s="99" t="s">
-        <v>56</v>
-      </c>
-      <c r="D29" s="100"/>
-      <c r="E29" s="170" t="s">
-        <v>80</v>
-      </c>
-      <c r="F29" s="171"/>
-      <c r="G29" s="172" t="s">
-        <v>81</v>
-      </c>
-      <c r="H29" s="172" t="s">
-        <v>82</v>
-      </c>
-      <c r="I29" s="138" t="s">
+      <c r="D29" s="166" t="s">
+        <v>84</v>
+      </c>
+      <c r="E29" s="169" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="170"/>
+      <c r="G29" s="171"/>
+      <c r="H29" s="171"/>
+      <c r="I29" s="133" t="s">
+        <v>86</v>
+      </c>
+      <c r="J29" s="173" t="s">
         <v>83</v>
       </c>
-      <c r="J29" s="174" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" ht="13.50" customHeight="1">
-      <c r="A30" s="165"/>
-      <c r="B30" s="167"/>
-      <c r="C30" s="124" t="s">
-        <v>84</v>
-      </c>
-      <c r="D30" s="176" t="s">
-        <v>85</v>
-      </c>
-      <c r="E30" s="177" t="s">
-        <v>86</v>
-      </c>
-      <c r="F30" s="179" t="s">
+    </row>
+    <row r="30" spans="1:10" ht="6.00" customHeight="1">
+      <c r="A30" s="157"/>
+      <c r="B30" s="160"/>
+      <c r="C30" s="164"/>
+      <c r="D30" s="167"/>
+      <c r="E30" s="175"/>
+      <c r="F30" s="175"/>
+      <c r="G30" s="112" t="s">
         <v>87</v>
       </c>
-      <c r="G30" s="117" t="s">
+      <c r="H30" s="178" t="s">
         <v>88</v>
       </c>
-      <c r="H30" s="182" t="s">
+      <c r="I30" s="134"/>
+      <c r="J30" s="174"/>
+    </row>
+    <row r="31" spans="1:10" ht="7.50" customHeight="1">
+      <c r="A31" s="180"/>
+      <c r="B31" s="180"/>
+      <c r="C31" s="180"/>
+      <c r="D31" s="69"/>
+      <c r="E31" s="176"/>
+      <c r="F31" s="176"/>
+      <c r="G31" s="114"/>
+      <c r="H31" s="179"/>
+      <c r="I31" s="182"/>
+      <c r="J31" s="182"/>
+    </row>
+    <row r="32" spans="1:10" ht="19.75" customHeight="1">
+      <c r="A32" s="181"/>
+      <c r="B32" s="181"/>
+      <c r="C32" s="181"/>
+      <c r="D32" s="64"/>
+      <c r="E32" s="183" t="s">
         <v>89</v>
       </c>
-      <c r="I30" s="139"/>
-      <c r="J30" s="175"/>
-    </row>
-    <row r="31" spans="1:10" ht="13.50" customHeight="1">
-      <c r="A31" s="184"/>
-      <c r="B31" s="48"/>
-      <c r="C31" s="124" t="s">
+      <c r="F32" s="183" t="s">
         <v>90</v>
       </c>
-      <c r="D31" s="176" t="s">
-        <v>85</v>
-      </c>
-      <c r="E31" s="178"/>
-      <c r="F31" s="180"/>
-      <c r="G31" s="119"/>
-      <c r="H31" s="183"/>
-      <c r="I31" s="186"/>
-      <c r="J31" s="186"/>
-    </row>
-    <row r="32" spans="1:10" ht="8.25" customHeight="1">
-      <c r="A32" s="185"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="99" t="s">
-        <v>68</v>
-      </c>
-      <c r="D32" s="100"/>
-      <c r="E32" s="188"/>
-      <c r="F32" s="188"/>
-      <c r="G32" s="49"/>
+      <c r="G32" s="184"/>
       <c r="H32" s="185"/>
       <c r="I32" s="185"/>
       <c r="J32" s="185"/>
-    </row>
-    <row r="33" spans="1:10" ht="13.50" customHeight="1">
-      <c r="A33" s="185"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="124" t="s">
-        <v>78</v>
-      </c>
-      <c r="D33" s="176" t="s">
-        <v>85</v>
-      </c>
-      <c r="E33" s="187"/>
-      <c r="F33" s="187"/>
-      <c r="G33" s="49"/>
-      <c r="H33" s="185"/>
-      <c r="I33" s="185"/>
-      <c r="J33" s="185"/>
     </row>
   </sheetData>
   <mergeCells count="94">
@@ -2782,7 +2770,7 @@
     <mergeCell ref="A5:A9"/>
     <mergeCell ref="B5:B9"/>
     <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F11"/>
+    <mergeCell ref="E6:F12"/>
     <mergeCell ref="G6:H6"/>
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="C8:D8"/>
@@ -2791,13 +2779,16 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="I10:J11"/>
+    <mergeCell ref="I10:J10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="B11:B14"/>
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="J11:J12"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F14"/>
-    <mergeCell ref="G12:H14"/>
-    <mergeCell ref="I12:J14"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="E13:F14"/>
+    <mergeCell ref="G13:H14"/>
+    <mergeCell ref="I13:J14"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="C16:D16"/>
@@ -2838,16 +2829,16 @@
     <mergeCell ref="G25:H25"/>
     <mergeCell ref="I25:I26"/>
     <mergeCell ref="J25:J26"/>
-    <mergeCell ref="C26:C28"/>
-    <mergeCell ref="D26:D28"/>
     <mergeCell ref="E26:E28"/>
     <mergeCell ref="F26:F28"/>
     <mergeCell ref="G26:H27"/>
     <mergeCell ref="A27:B27"/>
     <mergeCell ref="I27:J27"/>
-    <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="C29:D29"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="B28:B30"/>
+    <mergeCell ref="C28:D28"/>
+    <mergeCell ref="C29:C30"/>
+    <mergeCell ref="D29:D30"/>
     <mergeCell ref="E29:F29"/>
     <mergeCell ref="I29:I30"/>
     <mergeCell ref="J29:J30"/>
@@ -2855,12 +2846,9 @@
     <mergeCell ref="F30:F31"/>
     <mergeCell ref="G30:G31"/>
     <mergeCell ref="H30:H31"/>
-    <mergeCell ref="A31:B33"/>
+    <mergeCell ref="A31:D32"/>
     <mergeCell ref="I31:J31"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="E32:E33"/>
-    <mergeCell ref="F32:F33"/>
-    <mergeCell ref="G32:J33"/>
+    <mergeCell ref="G32:J32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
